--- a/Results/Wisconsin breast dataset/Wisconsin_gene_layouts.xlsx
+++ b/Results/Wisconsin breast dataset/Wisconsin_gene_layouts.xlsx
@@ -7,13 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mealpy_nystrom_global" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mealpy_nystrom_stratified" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mealpy_random" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="optuna_nystrom_global" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="optuna_nystrom_stratified" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="optuna_random" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="training_optuna_optuna_random_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="mealpy_nystrom_6030_60" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="mealpy_nystrom_global" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="mealpy_nystrom_stratified" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="mealpy_nystrom_stratified6030" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="mealpy_random" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="optuna_nystrom_6030_500" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="optuna_nystrom_global" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="optuna_nystrom_stratified" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="optuna_nystrom_stratified6030" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="optuna_random" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="training_optuna_optuna_random_1" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,17 +53,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6E8D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5C4A1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -515,7 +519,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.5708</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="3">
@@ -532,11 +536,11 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>RX</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3.1416</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="4">
@@ -551,9 +555,9 @@
       <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -572,13 +576,13 @@
       <c r="C5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.7854</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="6">
@@ -593,9 +597,9 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -614,13 +618,13 @@
       <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.1416</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="8">
@@ -635,13 +639,13 @@
       <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7854</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="9">
@@ -656,13 +660,13 @@
       <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.7854</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="10">
@@ -683,7 +687,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.7854</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="11">
@@ -698,13 +702,13 @@
       <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.1416</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="12">
@@ -719,13 +723,13 @@
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3.1416</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="13">
@@ -740,13 +744,13 @@
       <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.1416</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="14">
@@ -761,13 +765,13 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.1416</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="15">
@@ -782,13 +786,13 @@
       <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.3927</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="16">
@@ -803,9 +807,9 @@
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -824,13 +828,781 @@
       <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.3927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>gene</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>qubit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5.6937</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.0043</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>g3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3.661</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>g4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5.4213</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>g5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1.7962</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>g6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.4561</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>g7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5.9495</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>g8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5.5601</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>g9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.8426</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4.4902</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>g11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>g12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>5.9687</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>g13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
+      <c r="E14" s="2" t="n">
+        <v>2.0047</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>g14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6.271</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>g15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5.6378</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>g16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="n">
-        <v>1.5708</v>
+        <v>2.6646</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>gene</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>qubit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5.8316</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>2.9366</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>g3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3.0902</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>g4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1.3236</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>g5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2.3368</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>g6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2.9175</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>g7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.6748</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>g8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5.834</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>g9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4.9872</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>5.8407</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>g11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5.8581</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>g12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>5.9062</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>g13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4.615</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>g14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5.3587</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>g15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1.1034</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>g16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2.6939</v>
       </c>
     </row>
   </sheetData>
@@ -893,13 +1665,13 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.3927</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="3">
@@ -914,13 +1686,13 @@
       <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.5708</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="4">
@@ -935,13 +1707,13 @@
       <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7854</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="5">
@@ -958,11 +1730,11 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.5708</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="6">
@@ -977,13 +1749,13 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.5708</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="7">
@@ -998,9 +1770,9 @@
       <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -1019,13 +1791,13 @@
       <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.1416</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="9">
@@ -1040,13 +1812,13 @@
       <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.1416</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="10">
@@ -1061,13 +1833,13 @@
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.5708</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="11">
@@ -1082,9 +1854,9 @@
       <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1103,9 +1875,9 @@
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1124,13 +1896,13 @@
       <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.3927</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="14">
@@ -1145,9 +1917,9 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1166,13 +1938,13 @@
       <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>3.1416</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="16">
@@ -1187,13 +1959,13 @@
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>RZ</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.5708</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="17">
@@ -1208,13 +1980,13 @@
       <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.3927</v>
+        <v>1.5708</v>
       </c>
     </row>
   </sheetData>
@@ -1279,11 +2051,11 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3.1416</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="3">
@@ -1298,9 +2070,9 @@
       <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -1319,13 +2091,13 @@
       <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.5708</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="5">
@@ -1342,11 +2114,11 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>RX</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.7854</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="6">
@@ -1361,13 +2133,13 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>RY</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.1416</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="7">
@@ -1384,11 +2156,11 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>CNOT</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.7854</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="8">
@@ -1403,13 +2175,13 @@
       <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7854</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="9">
@@ -1424,9 +2196,9 @@
       <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -1445,13 +2217,13 @@
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>RY</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.1416</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="11">
@@ -1468,7 +2240,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>CNOT</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -1487,13 +2259,13 @@
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.3927</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="13">
@@ -1508,9 +2280,9 @@
       <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -1529,9 +2301,9 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1550,9 +2322,9 @@
       <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
@@ -1571,13 +2343,13 @@
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.3927</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="17">
@@ -1592,13 +2364,13 @@
       <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.5708</v>
+        <v>0.3927</v>
       </c>
     </row>
   </sheetData>
@@ -1661,13 +2433,13 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>CNOT</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.1505</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="3">
@@ -1688,7 +2460,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.3559</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="4">
@@ -1703,13 +2475,13 @@
       <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7029</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="5">
@@ -1730,7 +2502,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.612</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="6">
@@ -1745,13 +2517,13 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.4447</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="7">
@@ -1772,7 +2544,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.0665</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="8">
@@ -1787,13 +2559,13 @@
       <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.5442</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="9">
@@ -1814,7 +2586,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6.0707</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="10">
@@ -1831,11 +2603,11 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.6639</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="11">
@@ -1852,11 +2624,11 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>RZ</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.1622</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="12">
@@ -1871,13 +2643,13 @@
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.6502</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="13">
@@ -1898,7 +2670,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6.0804</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="14">
@@ -1913,13 +2685,13 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>RY</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>5.5942</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="15">
@@ -1936,11 +2708,11 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>RZ</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.5659</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="16">
@@ -1955,13 +2727,13 @@
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5.9244</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="17">
@@ -1976,13 +2748,13 @@
       <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.1943</v>
+        <v>3.1416</v>
       </c>
     </row>
   </sheetData>
@@ -2045,13 +2817,13 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0645</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="3">
@@ -2066,13 +2838,13 @@
       <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.6097</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="4">
@@ -2087,13 +2859,13 @@
       <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.462</v>
+        <v>1.5708</v>
       </c>
     </row>
     <row r="5">
@@ -2110,11 +2882,11 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>CNOT</t>
+          <t>RX</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.7657</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="6">
@@ -2129,13 +2901,13 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5421</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="7">
@@ -2150,13 +2922,13 @@
       <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5.4786</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="8">
@@ -2171,13 +2943,13 @@
       <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.2533</v>
+        <v>0.7854</v>
       </c>
     </row>
     <row r="9">
@@ -2192,13 +2964,13 @@
       <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5.5551</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="10">
@@ -2213,13 +2985,13 @@
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.6847</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="11">
@@ -2234,13 +3006,13 @@
       <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6.2325</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="12">
@@ -2257,11 +3029,11 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>RZ</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.9344</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="13">
@@ -2276,13 +3048,13 @@
       <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.8698</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="14">
@@ -2297,13 +3069,13 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.0567</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="15">
@@ -2318,13 +3090,13 @@
       <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.6982</v>
+        <v>3.1416</v>
       </c>
     </row>
     <row r="16">
@@ -2339,13 +3111,13 @@
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.853</v>
+        <v>0.3927</v>
       </c>
     </row>
     <row r="17">
@@ -2360,13 +3132,13 @@
       <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5.0926</v>
+        <v>1.5708</v>
       </c>
     </row>
   </sheetData>
@@ -2429,13 +3201,13 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5.6937</v>
+        <v>0.3833</v>
       </c>
     </row>
     <row r="3">
@@ -2450,13 +3222,13 @@
       <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0043</v>
+        <v>2.6336</v>
       </c>
     </row>
     <row r="4">
@@ -2471,13 +3243,13 @@
       <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.661</v>
+        <v>4.6837</v>
       </c>
     </row>
     <row r="5">
@@ -2492,13 +3264,13 @@
       <c r="C5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.4213</v>
+        <v>5.0696</v>
       </c>
     </row>
     <row r="6">
@@ -2515,11 +3287,11 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CNOT</t>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.7962</v>
+        <v>2.0687</v>
       </c>
     </row>
     <row r="7">
@@ -2534,13 +3306,13 @@
       <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>RZ</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4561</v>
+        <v>6.1115</v>
       </c>
     </row>
     <row r="8">
@@ -2557,11 +3329,11 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.9495</v>
+        <v>0.5954</v>
       </c>
     </row>
     <row r="9">
@@ -2578,11 +3350,11 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5.5601</v>
+        <v>2.9482</v>
       </c>
     </row>
     <row r="10">
@@ -2597,13 +3369,13 @@
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.8426</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="11">
@@ -2618,13 +3390,13 @@
       <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>RY</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.4902</v>
+        <v>1.6781</v>
       </c>
     </row>
     <row r="12">
@@ -2639,13 +3411,13 @@
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.01</v>
+        <v>1.3492</v>
       </c>
     </row>
     <row r="13">
@@ -2660,13 +3432,13 @@
       <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5.9687</v>
+        <v>1.9726</v>
       </c>
     </row>
     <row r="14">
@@ -2687,7 +3459,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2.0047</v>
+        <v>4.4084</v>
       </c>
     </row>
     <row r="15">
@@ -2702,13 +3474,13 @@
       <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>6.271</v>
+        <v>5.0144</v>
       </c>
     </row>
     <row r="16">
@@ -2723,13 +3495,13 @@
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5.6378</v>
+        <v>0.2616</v>
       </c>
     </row>
     <row r="17">
@@ -2744,13 +3516,13 @@
       <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.6646</v>
+        <v>5.9666</v>
       </c>
     </row>
   </sheetData>
@@ -2813,13 +3585,13 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5.8316</v>
+        <v>2.1505</v>
       </c>
     </row>
     <row r="3">
@@ -2834,13 +3606,13 @@
       <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>RX</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.9366</v>
+        <v>1.3559</v>
       </c>
     </row>
     <row r="4">
@@ -2855,13 +3627,13 @@
       <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.0902</v>
+        <v>0.7029</v>
       </c>
     </row>
     <row r="5">
@@ -2876,13 +3648,13 @@
       <c r="C5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.3236</v>
+        <v>5.612</v>
       </c>
     </row>
     <row r="6">
@@ -2897,13 +3669,13 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>RY</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.3368</v>
+        <v>4.4447</v>
       </c>
     </row>
     <row r="7">
@@ -2918,13 +3690,13 @@
       <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.9175</v>
+        <v>6.0665</v>
       </c>
     </row>
     <row r="8">
@@ -2939,13 +3711,13 @@
       <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>RY</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.6748</v>
+        <v>4.5442</v>
       </c>
     </row>
     <row r="9">
@@ -2960,13 +3732,13 @@
       <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>CNOT</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>5.834</v>
+        <v>6.0707</v>
       </c>
     </row>
     <row r="10">
@@ -2981,13 +3753,13 @@
       <c r="C10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.9872</v>
+        <v>3.6639</v>
       </c>
     </row>
     <row r="11">
@@ -3002,13 +3774,13 @@
       <c r="C11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>RY</t>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5.8407</v>
+        <v>1.1622</v>
       </c>
     </row>
     <row r="12">
@@ -3023,13 +3795,13 @@
       <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>5.8581</v>
+        <v>1.6502</v>
       </c>
     </row>
     <row r="13">
@@ -3044,13 +3816,13 @@
       <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5.9062</v>
+        <v>6.0804</v>
       </c>
     </row>
     <row r="14">
@@ -3065,13 +3837,13 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>RZ</t>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4.615</v>
+        <v>5.5942</v>
       </c>
     </row>
     <row r="15">
@@ -3086,13 +3858,13 @@
       <c r="C15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5.3587</v>
+        <v>0.5659</v>
       </c>
     </row>
     <row r="16">
@@ -3107,13 +3879,13 @@
       <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.1034</v>
+        <v>5.9244</v>
       </c>
     </row>
     <row r="17">
@@ -3128,13 +3900,781 @@
       <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>RZ</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.6939</v>
+        <v>1.1943</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>gene</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>qubit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.0645</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5.6097</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>g3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1.462</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>g4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3.7657</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>g5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.5421</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>g6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5.4786</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>g7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.2533</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>g8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5.5551</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>g9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.6847</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>6.2325</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>g11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4.9344</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>g12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2.8698</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>g13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1.0567</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>g14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2.6982</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>g15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4.853</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>g16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>5.0926</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>gene</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>layer</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>qubit</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>gate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>g1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5.5839</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>g2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>3.5861</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>g3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1.1554</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>g4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5.8653</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>g5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>RZ</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5.8229</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>g6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2.4262</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>g7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.6737</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>g8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5.2466</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>g9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4.1364</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>g10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2.7116</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>g11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5.9422</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>g12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4.7857</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>g13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5.5078</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>g14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4.6693</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>g15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>RX</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3.9936</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>g16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>CNOT</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1.7986</v>
       </c>
     </row>
   </sheetData>
